--- a/Data/a320 tăng cứng kiện.xlsx
+++ b/Data/a320 tăng cứng kiện.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AMECC JSC\Amecc 2\00. Overall Report\04.Assembly Part List\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB9A689-1BCE-4D9D-93C0-6AE81E2D80EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903D3768-BFDE-4D20-BEC9-1C909529A1D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-2530" windowWidth="25820" windowHeight="15500" xr2:uid="{5A2A4E05-4257-4DA7-BD56-707C6042B067}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5A2A4E05-4257-4DA7-BD56-707C6042B067}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="93">
   <si>
     <t>STT</t>
   </si>
@@ -301,6 +301,18 @@
   </si>
   <si>
     <t>PL16x136</t>
+  </si>
+  <si>
+    <t>SDM_A16_P1</t>
+  </si>
+  <si>
+    <t>PL1x115</t>
+  </si>
+  <si>
+    <t>A320-01-CP025_1</t>
+  </si>
+  <si>
+    <t>A320-01-CP025_2</t>
   </si>
 </sst>
 </file>
@@ -456,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -487,6 +499,18 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,16 +518,16 @@
   <dxfs count="12">
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
           <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -734,7 +758,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F4697BDB-34DC-4811-8729-51BC7A36CFF8}" name="Table36" displayName="Table36" ref="A91:J94" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F4697BDB-34DC-4811-8729-51BC7A36CFF8}" name="Table36" displayName="Table36" ref="A91:J94" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A91:J94" xr:uid="{F4697BDB-34DC-4811-8729-51BC7A36CFF8}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{CF19981B-2E64-4DAE-9F4A-F7F7FAADC70A}" name="STT"/>
@@ -1049,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C22614-0486-4942-B183-245307D55E54}">
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -3206,6 +3230,116 @@
         <v>46308</v>
       </c>
     </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="21"/>
+      <c r="B97" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" s="22"/>
+      <c r="D97" s="22"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="22">
+        <v>18</v>
+      </c>
+      <c r="G97" s="22">
+        <v>60</v>
+      </c>
+      <c r="H97" s="22"/>
+      <c r="I97" s="22"/>
+      <c r="J97" s="23"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="24">
+        <v>1</v>
+      </c>
+      <c r="B98" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C98" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D98" s="20">
+        <v>400</v>
+      </c>
+      <c r="E98" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98" s="20">
+        <v>3</v>
+      </c>
+      <c r="G98" s="20">
+        <v>10</v>
+      </c>
+      <c r="H98" s="20"/>
+      <c r="I98" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="J98" s="25">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="26">
+        <v>2</v>
+      </c>
+      <c r="B99" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C99" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D99" s="22">
+        <v>400</v>
+      </c>
+      <c r="E99" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99" s="22">
+        <v>15</v>
+      </c>
+      <c r="G99" s="22">
+        <v>50</v>
+      </c>
+      <c r="H99" s="22"/>
+      <c r="I99" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="J99" s="27">
+        <v>46312</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
